--- a/artfynd/A 35302-2021 artfynd.xlsx
+++ b/artfynd/A 35302-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35302-2021 artfynd.xlsx
+++ b/artfynd/A 35302-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95694851</v>
+        <v>95694847</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>353333.6440099777</v>
+        <v>353334</v>
       </c>
       <c r="R2" t="n">
-        <v>6469587.45037576</v>
+        <v>6469587</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,24 +751,14 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lockläte mm</t>
+          <t>Lockläte inifrån anmälan</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,32 +785,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95694847</v>
+        <v>95694851</v>
       </c>
       <c r="B3" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -848,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>353333.6440099777</v>
+        <v>353334</v>
       </c>
       <c r="R3" t="n">
-        <v>6469587.45037576</v>
+        <v>6469587</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -881,24 +861,14 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lockläte inifrån anmälan</t>
+          <t>Lockläte mm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,12 +898,7 @@
         <v>95694835</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>353333.6440099777</v>
+        <v>353334</v>
       </c>
       <c r="R4" t="n">
-        <v>6469587.45037576</v>
+        <v>6469587</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1006,19 +971,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
